--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31008,6 +31008,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1333">
+      <c r="A1333" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1333" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1333" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="G1333" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31031,6 +31031,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1334">
+      <c r="A1334" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1334" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>0.428999990224838</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>0.428999990224838</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>0.428999990224838</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>0.428999990224838</v>
+      </c>
+      <c r="G1334" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31054,6 +31054,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>0.430000007152557</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>0.409000009298325</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>0.430000007152557</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>0.409000009298325</v>
+      </c>
+      <c r="G1335" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31077,6 +31077,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1336" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G1336" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -30918,7 +30918,7 @@
     </row>
     <row r="1329">
       <c r="A1329" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1329" t="n">
         <v>0</v>
@@ -30941,7 +30941,7 @@
     </row>
     <row r="1330">
       <c r="A1330" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1330" t="n">
         <v>0</v>
@@ -30964,22 +30964,22 @@
     </row>
     <row r="1331">
       <c r="A1331" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1331" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C1331" t="n">
-        <v>0.404000014066696</v>
+        <v>0.41499999165535</v>
       </c>
       <c r="D1331" t="n">
-        <v>0.404000014066696</v>
+        <v>0.41499999165535</v>
       </c>
       <c r="E1331" t="n">
-        <v>0.404000014066696</v>
+        <v>0.41499999165535</v>
       </c>
       <c r="F1331" t="n">
-        <v>0.404000014066696</v>
+        <v>0.41499999165535</v>
       </c>
       <c r="G1331" t="s">
         <v>7</v>
@@ -30987,22 +30987,22 @@
     </row>
     <row r="1332">
       <c r="A1332" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1332" t="n">
-        <v>11000</v>
+        <v>500</v>
       </c>
       <c r="C1332" t="n">
-        <v>0.421999990940094</v>
+        <v>0.404000014066696</v>
       </c>
       <c r="D1332" t="n">
-        <v>0.409999996423721</v>
+        <v>0.404000014066696</v>
       </c>
       <c r="E1332" t="n">
-        <v>0.409999996423721</v>
+        <v>0.404000014066696</v>
       </c>
       <c r="F1332" t="n">
-        <v>0.421999990940094</v>
+        <v>0.404000014066696</v>
       </c>
       <c r="G1332" t="s">
         <v>7</v>
@@ -31010,19 +31010,19 @@
     </row>
     <row r="1333">
       <c r="A1333" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1333" t="n">
-        <v>500</v>
+        <v>11000</v>
       </c>
       <c r="C1333" t="n">
         <v>0.421999990940094</v>
       </c>
       <c r="D1333" t="n">
-        <v>0.421999990940094</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E1333" t="n">
-        <v>0.421999990940094</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="F1333" t="n">
         <v>0.421999990940094</v>
@@ -31033,22 +31033,22 @@
     </row>
     <row r="1334">
       <c r="A1334" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1334" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="C1334" t="n">
-        <v>0.428999990224838</v>
+        <v>0.421999990940094</v>
       </c>
       <c r="D1334" t="n">
-        <v>0.428999990224838</v>
+        <v>0.421999990940094</v>
       </c>
       <c r="E1334" t="n">
-        <v>0.428999990224838</v>
+        <v>0.421999990940094</v>
       </c>
       <c r="F1334" t="n">
-        <v>0.428999990224838</v>
+        <v>0.421999990940094</v>
       </c>
       <c r="G1334" t="s">
         <v>7</v>
@@ -31056,22 +31056,22 @@
     </row>
     <row r="1335">
       <c r="A1335" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1335" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C1335" t="n">
-        <v>0.430000007152557</v>
+        <v>0.428999990224838</v>
       </c>
       <c r="D1335" t="n">
-        <v>0.409000009298325</v>
+        <v>0.428999990224838</v>
       </c>
       <c r="E1335" t="n">
-        <v>0.430000007152557</v>
+        <v>0.428999990224838</v>
       </c>
       <c r="F1335" t="n">
-        <v>0.409000009298325</v>
+        <v>0.428999990224838</v>
       </c>
       <c r="G1335" t="s">
         <v>7</v>
@@ -31079,24 +31079,47 @@
     </row>
     <row r="1336">
       <c r="A1336" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1336" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C1336" t="n">
-        <v>0.400000005960464</v>
+        <v>0.430000007152557</v>
       </c>
       <c r="D1336" t="n">
-        <v>0.400000005960464</v>
+        <v>0.409000009298325</v>
       </c>
       <c r="E1336" t="n">
-        <v>0.400000005960464</v>
+        <v>0.430000007152557</v>
       </c>
       <c r="F1336" t="n">
-        <v>0.400000005960464</v>
+        <v>0.409000009298325</v>
       </c>
       <c r="G1336" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1337" t="n">
+        <v>84000</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>0.405000001192093</v>
+      </c>
+      <c r="G1337" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -35189,6 +35189,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1340" t="n">
+        <v>71000</v>
+      </c>
+      <c r="C1340" t="n">
+        <v>0.451999992132187</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>0.41100001335144</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="H1340" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -35197,7 +35197,7 @@
         <v>71000</v>
       </c>
       <c r="C1340" t="n">
-        <v>0.451999992132187</v>
+        <v>0.462000012397766</v>
       </c>
       <c r="D1340" t="n">
         <v>0.41100001335144</v>
@@ -35212,6 +35212,32 @@
         <v>0.462000012397766</v>
       </c>
       <c r="H1340" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1341" t="n">
+        <v>46500</v>
+      </c>
+      <c r="C1341" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>0.455000013113022</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>0.477999985218048</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>0.477999985218048</v>
+      </c>
+      <c r="H1341" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -35241,6 +35241,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1342" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1342" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="H1342" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -35267,6 +35267,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1343">
+      <c r="A1343" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1343" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1343" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>0.488999992609024</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>0.488999992609024</v>
+      </c>
+      <c r="H1343" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -35345,6 +35345,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1346">
+      <c r="A1346" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1346" t="n">
+        <v>38500</v>
+      </c>
+      <c r="C1346" t="n">
+        <v>0.526000022888184</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="H1346" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31392,8 +31392,31 @@
       <c r="E1349" t="n">
         <v>0.550000011920929</v>
       </c>
-      <c r="F1349"/>
+      <c r="F1349" t="n">
+        <v>0.583999991416931</v>
+      </c>
       <c r="G1349" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1350" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C1350" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>0.583999991416931</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>0.583999991416931</v>
+      </c>
+      <c r="F1350"/>
+      <c r="G1350" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31415,8 +31415,31 @@
       <c r="E1350" t="n">
         <v>0.583999991416931</v>
       </c>
-      <c r="F1350"/>
+      <c r="F1350" t="n">
+        <v>0.607999980449677</v>
+      </c>
       <c r="G1350" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1351" t="n">
+        <v>90500</v>
+      </c>
+      <c r="C1351" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>0.617999970912933</v>
+      </c>
+      <c r="F1351"/>
+      <c r="G1351" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31433,13 +31433,36 @@
         <v>0.639999985694885</v>
       </c>
       <c r="D1351" t="n">
-        <v>0.579999983310699</v>
+        <v>0.578000009059906</v>
       </c>
       <c r="E1351" t="n">
         <v>0.617999970912933</v>
       </c>
-      <c r="F1351"/>
+      <c r="F1351" t="n">
+        <v>0.578000009059906</v>
+      </c>
       <c r="G1351" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1352" t="n">
+        <v>44000</v>
+      </c>
+      <c r="C1352" t="n">
+        <v>0.59799998998642</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>0.544000029563904</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F1352"/>
+      <c r="G1352" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31461,8 +31461,31 @@
       <c r="E1352" t="n">
         <v>0.560000002384186</v>
       </c>
-      <c r="F1352"/>
+      <c r="F1352" t="n">
+        <v>0.544000029563904</v>
+      </c>
       <c r="G1352" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1353" t="n">
+        <v>15500</v>
+      </c>
+      <c r="C1353" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>0.508000016212463</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>0.527999997138977</v>
+      </c>
+      <c r="F1353"/>
+      <c r="G1353" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -31491,6 +31491,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1354" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1354" t="n">
+        <v>0.512000024318695</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>0.512000024318695</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>0.512000024318695</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>0.512000024318695</v>
+      </c>
+      <c r="G1354" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -35613,7 +35613,7 @@
         <v>37500</v>
       </c>
       <c r="C1356" t="n">
-        <v>0.476999998092651</v>
+        <v>0.48199999332428</v>
       </c>
       <c r="D1356" t="n">
         <v>0.448000013828278</v>
@@ -35628,6 +35628,32 @@
         <v>0.48199999332428</v>
       </c>
       <c r="H1356" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1357" t="n">
+        <v>30500</v>
+      </c>
+      <c r="C1357" t="n">
+        <v>0.522000014781952</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>0.483999997377396</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="H1357" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -35657,6 +35657,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1358" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1358" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="H1358" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39789,6 +39789,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1360">
+      <c r="A1360" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1360" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1360" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>500</v>
+      </c>
+      <c r="I1360" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39818,6 +39818,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1361">
+      <c r="A1361" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1361" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1361" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I1361" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39847,6 +39847,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1362">
+      <c r="A1362" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1362" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1362" t="n">
+        <v>0.402999997138977</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H1362" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1362" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39876,6 +39876,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1363">
+      <c r="A1363" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1363" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1363" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="H1363" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I1363" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39905,6 +39905,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1364">
+      <c r="A1364" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1364" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1364" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>0.430000007152557</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>0.423000007867813</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>0.423000007867813</v>
+      </c>
+      <c r="H1364" t="n">
+        <v>67500</v>
+      </c>
+      <c r="I1364" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39934,6 +39934,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1365">
+      <c r="A1365" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1365" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1365" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>0.430000007152557</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>0.41499999165535</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>0.41499999165535</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>43000</v>
+      </c>
+      <c r="I1365" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39963,6 +39963,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1366">
+      <c r="A1366" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1366" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1366" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="H1366" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I1366" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -39992,6 +39992,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1367">
+      <c r="A1367" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1367" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1367" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>0.418999999761581</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="H1367" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I1367" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ATON.MI.xlsx
+++ b/data/ATON.MI.xlsx
@@ -40021,6 +40021,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1368">
+      <c r="A1368" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1368" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="H1368" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I1368" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
